--- a/2_Course/3_Term/Math_Statistics/lab_02/ЛР2_Заварзин_ИИб-25-6-о.xlsx
+++ b/2_Course/3_Term/Math_Statistics/lab_02/ЛР2_Заварзин_ИИб-25-6-о.xlsx
@@ -190,13 +190,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -3732,7 +3730,7 @@
     <col min="10" max="10" width="9.140625" style="3"/>
     <col min="11" max="11" width="17" customWidth="1"/>
     <col min="12" max="12" width="16.85546875" customWidth="1"/>
-    <col min="15" max="15" width="9.140625" style="5"/>
+    <col min="15" max="15" width="9.140625" style="3"/>
     <col min="16" max="16" width="18" customWidth="1"/>
     <col min="17" max="17" width="18.140625" customWidth="1"/>
     <col min="20" max="20" width="9.140625" style="3"/>
@@ -3779,7 +3777,7 @@
       <c r="N1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="O1" s="4"/>
+      <c r="O1" s="2"/>
       <c r="P1" s="1" t="s">
         <v>3</v>
       </c>
@@ -9000,7 +8998,7 @@
         <v>5.9349933298382576</v>
       </c>
       <c r="N3">
-        <f t="shared" ref="N3:N8" si="4">(B3-1)*F3/_xlfn.CHISQ.INV.RT(0.975,B3-1)</f>
+        <f t="shared" ref="N3:N7" si="4">(B3-1)*F3/_xlfn.CHISQ.INV.RT(0.975,B3-1)</f>
         <v>41.808783510979168</v>
       </c>
     </row>
@@ -9048,7 +9046,7 @@
         <v>8.8397077667372628</v>
       </c>
       <c r="L4">
-        <f t="shared" ref="L3:L7" si="5">(B4-1)*F4/_xlfn.CHISQ.INV.RT(0.975,B4-1)-(B4-1)*F4/_xlfn.CHISQ.INV.RT(0.025,B4-1)</f>
+        <f t="shared" ref="L4:L7" si="5">(B4-1)*F4/_xlfn.CHISQ.INV.RT(0.975,B4-1)-(B4-1)*F4/_xlfn.CHISQ.INV.RT(0.025,B4-1)</f>
         <v>10.463492725006308</v>
       </c>
       <c r="M4">

--- a/2_Course/3_Term/Math_Statistics/lab_02/ЛР2_Заварзин_ИИб-25-6-о.xlsx
+++ b/2_Course/3_Term/Math_Statistics/lab_02/ЛР2_Заварзин_ИИб-25-6-о.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\SevSU\2_Course\3_Term\Math_Statistics\lab_02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB415496-8F86-474C-8603-6939EBDEDD9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B094EAD6-18D8-4111-80CD-2BB5CF2F1DBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Генеральная совокупность" sheetId="1" r:id="rId1"/>
